--- a/outputs/01a0719b-f374-7590-b5ae-261ff64e352b/visitors-2026-27.xlsx
+++ b/outputs/01a0719b-f374-7590-b5ae-261ff64e352b/visitors-2026-27.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visitors" sheetId="1" r:id="R7d008009120146eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visitors" sheetId="1" r:id="R9372025ecd8e46ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1375,7 +1375,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c2df986735b4f9b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R374c5433d2cf4a62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a0719b-f374-7590-b5ae-261ff64e352b/visitors-2026-27.xlsx
+++ b/outputs/01a0719b-f374-7590-b5ae-261ff64e352b/visitors-2026-27.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visitors" sheetId="1" r:id="R9372025ecd8e46ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visitors" sheetId="1" r:id="Rbd757cac8ebe4d37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -87,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -134,6 +134,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -141,7 +142,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -410,7 +411,7 @@
       </x:c>
       <x:c r="F2" s="7" t="str"/>
       <x:c r="G2" s="13" t="str">
-        <x:v>Stephen Hansen's Office</x:v>
+        <x:v>Drayton House 116</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -428,7 +429,9 @@
         <x:v>46353</x:v>
       </x:c>
       <x:c r="F3" s="8" t="str"/>
-      <x:c r="G3" s="14" t="str"/>
+      <x:c r="G3" s="14" t="str">
+        <x:v>Drayton House 106</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="8" t="str">
@@ -1333,12 +1336,18 @@
         <x:v>Northwestern University</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str"/>
-      <x:c r="D55" s="12"/>
-      <x:c r="E55" s="12"/>
-      <x:c r="F55" s="9" t="str">
-        <x:v>November 2026 (dates TBA)</x:v>
-      </x:c>
+      <x:c r="D55" s="12" t="n">
+        <x:v>46342</x:v>
+      </x:c>
+      <x:c r="E55" s="12" t="n">
+        <x:v>46360</x:v>
+      </x:c>
+      <x:c r="F55" s="9" t="str"/>
       <x:c r="G55" s="15" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="D56" s="18"/>
+      <x:c r="E56" s="18"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="16" t="str">
@@ -1347,6 +1356,8 @@
       <x:c r="B57" s="17" t="str">
         <x:v>This workbook is the manually maintained source for the Visitors webpage. Yellow cells need information; blue Office cells are optional.</x:v>
       </x:c>
+      <x:c r="D57" s="18"/>
+      <x:c r="E57" s="18"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="16" t="str">
@@ -1355,6 +1366,8 @@
       <x:c r="B58" s="17" t="str">
         <x:v>Use Start date and End date when known. Use Date display only for an approximate period such as “November 2026 (dates TBA)”.</x:v>
       </x:c>
+      <x:c r="D58" s="18"/>
+      <x:c r="E58" s="18"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="16" t="str">
@@ -1363,6 +1376,8 @@
       <x:c r="B59" s="17" t="str">
         <x:v>UCL Economics Research seminar schedule and updates supplied by the project owner.</x:v>
       </x:c>
+      <x:c r="D59" s="18"/>
+      <x:c r="E59" s="18"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="C2:C55">
@@ -1375,7 +1390,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R374c5433d2cf4a62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re546fd646cfb443e"/>
   </x:tableParts>
 </x:worksheet>
 </file>